--- a/策划文档/参考文档/玩法交互界面.xlsx
+++ b/策划文档/参考文档/玩法交互界面.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cardgame\策划文档\参考文档\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5604C68-11B9-49E3-86CD-42EA6E4FBCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="界面" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,13 +25,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +66,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +79,79 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>533400</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>18</xdr:col>
+          <xdr:colOff>400050</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Object 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A36B277-09EE-29BD-B27A-A052ED512B6F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+            <a:extLst>
+              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+                <a14:hiddenEffects>
+                  <a:effectLst>
+                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                      <a:srgbClr val="808080"/>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </a14:hiddenEffects>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +416,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Visio.Drawing.15" shapeId="1025" r:id="rId4">
+          <objectPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>533400</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>18</xdr:col>
+                <xdr:colOff>400050</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Visio.Drawing.15" shapeId="1025" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
 </worksheet>
 </file>